--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476147</v>
+        <v>122476141</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432464</v>
+        <v>432394</v>
       </c>
       <c r="R8" t="n">
-        <v>7055854</v>
+        <v>7055947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476141</v>
+        <v>122476147</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432394</v>
+        <v>432464</v>
       </c>
       <c r="R9" t="n">
-        <v>7055947</v>
+        <v>7055854</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122476163</v>
+        <v>122476152</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432591</v>
+        <v>432542</v>
       </c>
       <c r="R2" t="n">
-        <v>7055967</v>
+        <v>7055883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122476165</v>
+        <v>122476144</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432636</v>
+        <v>432408</v>
       </c>
       <c r="R3" t="n">
-        <v>7055976</v>
+        <v>7055832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122476143</v>
+        <v>122476150</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432389</v>
+        <v>432553</v>
       </c>
       <c r="R4" t="n">
-        <v>7055824</v>
+        <v>7055867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122476152</v>
+        <v>122476163</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432542</v>
+        <v>432591</v>
       </c>
       <c r="R5" t="n">
-        <v>7055883</v>
+        <v>7055967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122476144</v>
+        <v>122476143</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432408</v>
+        <v>432389</v>
       </c>
       <c r="R6" t="n">
-        <v>7055832</v>
+        <v>7055824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122476149</v>
+        <v>122476121</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57425</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1243,17 +1243,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432520</v>
+        <v>432643</v>
       </c>
       <c r="R7" t="n">
-        <v>7055827</v>
+        <v>7055991</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1302,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>Sittande i toppen av en gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476141</v>
+        <v>122476165</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432394</v>
+        <v>432636</v>
       </c>
       <c r="R8" t="n">
-        <v>7055947</v>
+        <v>7055976</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1409,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476147</v>
+        <v>122476162</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432464</v>
+        <v>432500</v>
       </c>
       <c r="R9" t="n">
-        <v>7055854</v>
+        <v>7055837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1543,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122476150</v>
+        <v>122476147</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1571,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432553</v>
+        <v>432464</v>
       </c>
       <c r="R10" t="n">
-        <v>7055867</v>
+        <v>7055854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122476140</v>
+        <v>122476149</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432442</v>
+        <v>432520</v>
       </c>
       <c r="R11" t="n">
-        <v>7056074</v>
+        <v>7055827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1730,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122476166</v>
+        <v>122476140</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1779,24 +1791,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432680</v>
+        <v>432442</v>
       </c>
       <c r="R12" t="n">
-        <v>7056038</v>
+        <v>7056074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1837,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera troliga bohål  i björk på ca 4-6m h.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122476146</v>
+        <v>122476160</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,21 +1880,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432398</v>
+        <v>432455</v>
       </c>
       <c r="R13" t="n">
-        <v>7055834</v>
+        <v>7055846</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1944,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122476160</v>
+        <v>122476146</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432455</v>
+        <v>432398</v>
       </c>
       <c r="R14" t="n">
-        <v>7055846</v>
+        <v>7055834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2051,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,7 +2078,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122476154</v>
+        <v>122476166</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2107,29 +2111,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432629</v>
+        <v>432680</v>
       </c>
       <c r="R15" t="n">
-        <v>7055987</v>
+        <v>7056038</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Observerades sittandes i en topp och avge läten en kort minut, med hökuggla i närheten.</t>
+          <t>Flera troliga bohål  i björk på ca 4-6m h.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122476156</v>
+        <v>122476141</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432679</v>
+        <v>432394</v>
       </c>
       <c r="R16" t="n">
-        <v>7056287</v>
+        <v>7055947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122476162</v>
+        <v>122476154</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,34 +2316,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432500</v>
+        <v>432629</v>
       </c>
       <c r="R17" t="n">
-        <v>7055837</v>
+        <v>7055987</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Observerades sittandes i en topp och avge läten en kort minut, med hökuggla i närheten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,7 +2422,7 @@
         <v>122476159</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,10 +2526,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122476121</v>
+        <v>122476156</v>
       </c>
       <c r="B19" t="n">
-        <v>57425</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,50 +2538,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102620</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432643</v>
+        <v>432679</v>
       </c>
       <c r="R19" t="n">
-        <v>7055991</v>
+        <v>7056287</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sittande i toppen av en gran</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122476152</v>
+        <v>122476165</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432542</v>
+        <v>432636</v>
       </c>
       <c r="R2" t="n">
-        <v>7055883</v>
+        <v>7055976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122476144</v>
+        <v>122476146</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432408</v>
+        <v>432398</v>
       </c>
       <c r="R3" t="n">
-        <v>7055832</v>
+        <v>7055834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122476150</v>
+        <v>122476160</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432553</v>
+        <v>432455</v>
       </c>
       <c r="R4" t="n">
-        <v>7055867</v>
+        <v>7055846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122476163</v>
+        <v>122476152</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432591</v>
+        <v>432542</v>
       </c>
       <c r="R5" t="n">
-        <v>7055967</v>
+        <v>7055883</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122476143</v>
+        <v>122476154</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1136,17 +1136,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432389</v>
+        <v>432629</v>
       </c>
       <c r="R6" t="n">
-        <v>7055824</v>
+        <v>7055987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>Observerades sittandes i en topp och avge läten en kort minut, med hökuggla i närheten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122476121</v>
+        <v>122476140</v>
       </c>
       <c r="B7" t="n">
-        <v>57425</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,20 +1234,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1243,29 +1255,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432643</v>
+        <v>432442</v>
       </c>
       <c r="R7" t="n">
-        <v>7055991</v>
+        <v>7056074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sittande i toppen av en gran</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476165</v>
+        <v>122476163</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432636</v>
+        <v>432591</v>
       </c>
       <c r="R8" t="n">
-        <v>7055976</v>
+        <v>7055967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476162</v>
+        <v>122476143</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432500</v>
+        <v>432389</v>
       </c>
       <c r="R9" t="n">
-        <v>7055837</v>
+        <v>7055824</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122476147</v>
+        <v>122476162</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432464</v>
+        <v>432500</v>
       </c>
       <c r="R10" t="n">
-        <v>7055854</v>
+        <v>7055837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122476149</v>
+        <v>122476166</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1684,16 +1684,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432520</v>
+        <v>432680</v>
       </c>
       <c r="R11" t="n">
-        <v>7055827</v>
+        <v>7056038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1738,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>Flera troliga bohål  i björk på ca 4-6m h.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122476140</v>
+        <v>122476147</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1797,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432442</v>
+        <v>432464</v>
       </c>
       <c r="R12" t="n">
-        <v>7056074</v>
+        <v>7055854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122476160</v>
+        <v>122476150</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1904,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432455</v>
+        <v>432553</v>
       </c>
       <c r="R13" t="n">
-        <v>7055846</v>
+        <v>7055867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122476146</v>
+        <v>122476149</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2011,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432398</v>
+        <v>432520</v>
       </c>
       <c r="R14" t="n">
-        <v>7055834</v>
+        <v>7055827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2059,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122476166</v>
+        <v>122476159</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,42 +2102,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432680</v>
+        <v>432498</v>
       </c>
       <c r="R15" t="n">
-        <v>7056038</v>
+        <v>7056087</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera troliga bohål  i björk på ca 4-6m h.</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122476141</v>
+        <v>122476156</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432394</v>
+        <v>432679</v>
       </c>
       <c r="R16" t="n">
-        <v>7055947</v>
+        <v>7056287</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122476154</v>
+        <v>122476121</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57425</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,20 +2312,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432629</v>
+        <v>432643</v>
       </c>
       <c r="R17" t="n">
-        <v>7055987</v>
+        <v>7055991</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Observerades sittandes i en topp och avge läten en kort minut, med hökuggla i närheten.</t>
+          <t>Sittande i toppen av en gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122476159</v>
+        <v>122476144</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432498</v>
+        <v>432408</v>
       </c>
       <c r="R18" t="n">
-        <v>7056087</v>
+        <v>7055832</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122476156</v>
+        <v>122476141</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432679</v>
+        <v>432394</v>
       </c>
       <c r="R19" t="n">
-        <v>7056287</v>
+        <v>7055947</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122476146</v>
+        <v>122476141</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432398</v>
+        <v>432394</v>
       </c>
       <c r="R3" t="n">
-        <v>7055834</v>
+        <v>7055947</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122476160</v>
+        <v>122476143</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432455</v>
+        <v>432389</v>
       </c>
       <c r="R4" t="n">
-        <v>7055846</v>
+        <v>7055824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122476152</v>
+        <v>122476156</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432542</v>
+        <v>432679</v>
       </c>
       <c r="R5" t="n">
-        <v>7055883</v>
+        <v>7056287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122476154</v>
+        <v>122476121</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57425</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,20 +1115,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432629</v>
+        <v>432643</v>
       </c>
       <c r="R6" t="n">
-        <v>7055987</v>
+        <v>7055991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Observerades sittandes i en topp och avge läten en kort minut, med hökuggla i närheten.</t>
+          <t>Sittande i toppen av en gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122476140</v>
+        <v>122476160</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432442</v>
+        <v>432455</v>
       </c>
       <c r="R7" t="n">
-        <v>7056074</v>
+        <v>7055846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122476163</v>
+        <v>122476149</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432591</v>
+        <v>432520</v>
       </c>
       <c r="R8" t="n">
-        <v>7055967</v>
+        <v>7055827</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122476143</v>
+        <v>122476159</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432389</v>
+        <v>432498</v>
       </c>
       <c r="R9" t="n">
-        <v>7055824</v>
+        <v>7056087</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122476166</v>
+        <v>122476147</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1684,24 +1684,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432680</v>
+        <v>432464</v>
       </c>
       <c r="R11" t="n">
-        <v>7056038</v>
+        <v>7055854</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1730,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera troliga bohål  i björk på ca 4-6m h.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122476147</v>
+        <v>122476150</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1805,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432464</v>
+        <v>432553</v>
       </c>
       <c r="R12" t="n">
-        <v>7055854</v>
+        <v>7055867</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1837,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1864,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122476150</v>
+        <v>122476154</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1905,17 +1897,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432553</v>
+        <v>432629</v>
       </c>
       <c r="R13" t="n">
-        <v>7055867</v>
+        <v>7055987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Observerades sittandes i en topp och avge läten en kort minut, med hökuggla i närheten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122476149</v>
+        <v>122476146</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2019,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432520</v>
+        <v>432398</v>
       </c>
       <c r="R14" t="n">
-        <v>7055827</v>
+        <v>7055834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122476159</v>
+        <v>122476166</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,34 +2106,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432498</v>
+        <v>432680</v>
       </c>
       <c r="R15" t="n">
-        <v>7056087</v>
+        <v>7056038</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2178,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>Flera troliga bohål  i björk på ca 4-6m h.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122476156</v>
+        <v>122476140</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432679</v>
+        <v>432442</v>
       </c>
       <c r="R16" t="n">
-        <v>7056287</v>
+        <v>7056074</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2285,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>mycket rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122476121</v>
+        <v>122476152</v>
       </c>
       <c r="B17" t="n">
-        <v>57425</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,20 +2324,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102620</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2333,29 +2345,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hömyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432643</v>
+        <v>432542</v>
       </c>
       <c r="R17" t="n">
-        <v>7055991</v>
+        <v>7055883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Sittande i toppen av en gran</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122476141</v>
+        <v>122476163</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432394</v>
+        <v>432591</v>
       </c>
       <c r="R19" t="n">
-        <v>7055947</v>
+        <v>7055967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>122476121</v>
       </c>
       <c r="B6" t="n">
-        <v>57425</v>
+        <v>57428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>122476121</v>
       </c>
       <c r="B6" t="n">
-        <v>57428</v>
+        <v>57434</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>122476121</v>
       </c>
       <c r="B6" t="n">
-        <v>57434</v>
+        <v>57437</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52547-2024 artfynd.xlsx
+++ b/artfynd/A 52547-2024 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>122476121</v>
       </c>
       <c r="B6" t="n">
-        <v>57437</v>
+        <v>57438</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
